--- a/dcf/TRP.xlsx
+++ b/dcf/TRP.xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1099,25 +1099,25 @@
         </is>
       </c>
       <c r="B4" s="51" t="n">
-        <v>0.04770027247564632</v>
+        <v>0.04803460027774664</v>
       </c>
       <c r="C4" s="51" t="n">
-        <v>0.05270027247564631</v>
+        <v>0.05303460027774664</v>
       </c>
       <c r="D4" s="51" t="n">
-        <v>0.05770027247564632</v>
+        <v>0.05803460027774664</v>
       </c>
       <c r="E4" s="51" t="n">
-        <v>0.06270027247564632</v>
+        <v>0.06303460027774664</v>
       </c>
       <c r="F4" s="51" t="n">
-        <v>0.06770027247564632</v>
+        <v>0.06803460027774665</v>
       </c>
       <c r="G4" s="51" t="n">
-        <v>0.07270027247564631</v>
+        <v>0.07303460027774664</v>
       </c>
       <c r="H4" s="51" t="n">
-        <v>0.07770027247564631</v>
+        <v>0.07803460027774664</v>
       </c>
     </row>
     <row r="5">
@@ -1125,25 +1125,25 @@
         <v>9</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>29.14651600178922</v>
+        <v>28.94543613819421</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>26.20876113713049</v>
+        <v>26.01753965513143</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>23.41467734002011</v>
+        <v>23.23278046274361</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>20.75650352174944</v>
+        <v>20.58342888544253</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>18.22693432631507</v>
+        <v>18.06220898988343</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>15.81909131596893</v>
+        <v>15.66226990539071</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>13.5264961051174</v>
+        <v>13.3771590830146</v>
       </c>
     </row>
     <row r="6">
@@ -1151,25 +1151,25 @@
         <v>10</v>
       </c>
       <c r="B6" s="53" t="n">
-        <v>34.87347186941965</v>
+        <v>34.6541489598302</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>31.66944521410603</v>
+        <v>31.46091136282883</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>28.62264456771234</v>
+        <v>28.42431444276614</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>25.72455955734793</v>
+        <v>25.53588231950377</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>22.96718020653558</v>
+        <v>22.78763732165278</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>20.34296526676095</v>
+        <v>20.17206846646642</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>17.84481269187651</v>
+        <v>17.68210207189298</v>
       </c>
     </row>
     <row r="7">
@@ -1177,25 +1177,25 @@
         <v>11</v>
       </c>
       <c r="B7" s="53" t="n">
-        <v>40.60042773705009</v>
+        <v>40.3628617814662</v>
       </c>
       <c r="C7" s="53" t="n">
-        <v>37.13012929108155</v>
+        <v>36.90428307052624</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>33.83061179540459</v>
+        <v>33.61584842278867</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>30.69261559294644</v>
+        <v>30.488335753565</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>27.70742608675608</v>
+        <v>27.51306565342213</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>24.86683921755299</v>
+        <v>24.68186702754213</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>22.16312927863563</v>
+        <v>21.98704506077135</v>
       </c>
     </row>
     <row r="8">
@@ -1203,25 +1203,25 @@
         <v>12</v>
       </c>
       <c r="B8" s="53" t="n">
-        <v>46.32738360468053</v>
+        <v>46.0715746031022</v>
       </c>
       <c r="C8" s="53" t="n">
-        <v>42.59081336805708</v>
+        <v>42.34765477822363</v>
       </c>
       <c r="D8" s="53" t="n">
-        <v>39.03857902309682</v>
+        <v>38.80738240281121</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>35.66067162854493</v>
+        <v>35.44078918762624</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>32.44767196697659</v>
+        <v>32.23849398519147</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>29.39071316834502</v>
+        <v>29.19166558861783</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>26.48144586539474</v>
+        <v>26.29198804964973</v>
       </c>
     </row>
     <row r="9">
@@ -1229,25 +1229,25 @@
         <v>13</v>
       </c>
       <c r="B9" s="53" t="n">
-        <v>52.05433947231096</v>
+        <v>51.7802874247382</v>
       </c>
       <c r="C9" s="53" t="n">
-        <v>48.0514974450326</v>
+        <v>47.79102648592103</v>
       </c>
       <c r="D9" s="53" t="n">
-        <v>44.24654625078905</v>
+        <v>43.99891638283374</v>
       </c>
       <c r="E9" s="53" t="n">
-        <v>40.62872766414342</v>
+        <v>40.39324262168747</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>37.18791784719709</v>
+        <v>36.9639223169608</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>33.91458711913704</v>
+        <v>33.70146414969354</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>30.79976245215384</v>
+        <v>30.59693103852809</v>
       </c>
     </row>
     <row r="10">
@@ -1255,25 +1255,25 @@
         <v>14</v>
       </c>
       <c r="B10" s="53" t="n">
-        <v>57.78129533994142</v>
+        <v>57.48900024637419</v>
       </c>
       <c r="C10" s="53" t="n">
-        <v>53.51218152200814</v>
+        <v>53.23439819361845</v>
       </c>
       <c r="D10" s="53" t="n">
-        <v>49.45451347848128</v>
+        <v>49.19045036285629</v>
       </c>
       <c r="E10" s="53" t="n">
-        <v>45.59678369974192</v>
+        <v>45.34569605574871</v>
       </c>
       <c r="F10" s="53" t="n">
-        <v>41.92816372741762</v>
+        <v>41.68935064873016</v>
       </c>
       <c r="G10" s="53" t="n">
-        <v>38.43846106992908</v>
+        <v>38.21126271076926</v>
       </c>
       <c r="H10" s="53" t="n">
-        <v>35.11807903891297</v>
+        <v>34.90187402740648</v>
       </c>
     </row>
     <row r="11">
@@ -1281,25 +1281,25 @@
         <v>15</v>
       </c>
       <c r="B11" s="53" t="n">
-        <v>63.50825120757184</v>
+        <v>63.1977130680102</v>
       </c>
       <c r="C11" s="53" t="n">
-        <v>58.97286559898367</v>
+        <v>58.67776990131586</v>
       </c>
       <c r="D11" s="53" t="n">
-        <v>54.66248070617351</v>
+        <v>54.38198434287882</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>50.56483973534041</v>
+        <v>50.29814948980995</v>
       </c>
       <c r="F11" s="53" t="n">
-        <v>46.66840960763813</v>
+        <v>46.4147789804995</v>
       </c>
       <c r="G11" s="53" t="n">
-        <v>42.96233502072109</v>
+        <v>42.72106127184497</v>
       </c>
       <c r="H11" s="53" t="n">
-        <v>39.43639562567208</v>
+        <v>39.20681701628486</v>
       </c>
     </row>
     <row r="13">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="B13" s="53" t="n">
-        <v>66.47000122070312</v>
+        <v>68.19999694824219</v>
       </c>
     </row>
     <row r="14">
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B14" s="55" t="n">
-        <v>0.06270027247564632</v>
+        <v>0.06303460027774664</v>
       </c>
       <c r="C14" s="56" t="n">
         <v>12</v>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>0.6512626635733594</v>
+        <v>0.6509082256301336</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24404,7 +24404,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>66.47000122070312</v>
+        <v>68.19999694824219</v>
       </c>
     </row>
     <row r="49">
@@ -24566,13 +24566,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>35.66067162854493</v>
+        <v>35.44078918762624</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>62.68411958766829</v>
+        <v>62.38376599677384</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>14.28773905346399</v>
+        <v>14.13100652924117</v>
       </c>
     </row>
     <row r="59">
